--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488158_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488158_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.0416</v>
+        <v>8.953799999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>9.0505</v>
+        <v>6.5044</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9911</v>
+        <v>2.4494</v>
       </c>
       <c r="G2" t="n">
         <v>4.0593</v>
@@ -610,13 +610,13 @@
         <v>2.2234</v>
       </c>
       <c r="S2" t="n">
-        <v>4.9823</v>
+        <v>1.8945</v>
       </c>
       <c r="T2" t="n">
-        <v>4.4482</v>
+        <v>1.902</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5342</v>
+        <v>-0.0075</v>
       </c>
       <c r="V2" t="n">
         <v>1.8883</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.539099999999999</v>
+        <v>8.9084</v>
       </c>
       <c r="E3" t="n">
         <v>5.6018</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9372</v>
+        <v>3.3066</v>
       </c>
       <c r="G3" t="n">
         <v>5.0745</v>
@@ -688,13 +688,13 @@
         <v>3.1499</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6677999999999999</v>
+        <v>1.0371</v>
       </c>
       <c r="T3" t="n">
         <v>1.0744</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4066</v>
+        <v>-0.0373</v>
       </c>
       <c r="V3" t="n">
         <v>0.9439</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.9713</v>
+        <v>6.4123</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6847</v>
+        <v>5.0764</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2866</v>
+        <v>1.3358</v>
       </c>
       <c r="G4" t="n">
         <v>5.7706</v>
@@ -766,13 +766,13 @@
         <v>2.0382</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7257</v>
+        <v>-0.2848</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4166</v>
+        <v>-0.0249</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3092</v>
+        <v>-0.2599</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.113</v>
+        <v>5.578</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5662</v>
+        <v>2.0559</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5468</v>
+        <v>3.5222</v>
       </c>
       <c r="G5" t="n">
         <v>6.4898</v>
@@ -844,13 +844,13 @@
         <v>1.297</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2733</v>
+        <v>0.7383</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2151</v>
+        <v>0.7048</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0582</v>
+        <v>0.0335</v>
       </c>
       <c r="V5" t="n">
         <v>0.9439</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.5565</v>
+        <v>4.3847</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6388</v>
+        <v>2.5409</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9176</v>
+        <v>1.8438</v>
       </c>
       <c r="G6" t="n">
         <v>4.5846</v>
@@ -922,13 +922,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>0.325</v>
+        <v>0.1533</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3246</v>
+        <v>0.2266</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0005</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>0.9439</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.6564</v>
+        <v>4.221</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4202</v>
+        <v>2.714</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2362</v>
+        <v>1.507</v>
       </c>
       <c r="G7" t="n">
         <v>0.09420000000000001</v>
@@ -1000,13 +1000,13 @@
         <v>1.8529</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6357</v>
+        <v>1.2003</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4551</v>
+        <v>0.7489</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1806</v>
+        <v>0.4514</v>
       </c>
       <c r="V7" t="n">
         <v>1.2589</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.5047</v>
+        <v>4.1661</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5805</v>
+        <v>2.1681</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9242</v>
+        <v>1.998</v>
       </c>
       <c r="G8" t="n">
         <v>4.3272</v>
@@ -1078,13 +1078,13 @@
         <v>1.8529</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9157999999999999</v>
+        <v>-0.2543</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3619</v>
+        <v>0.2257</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-0.48</v>
       </c>
       <c r="V8" t="n">
         <v>-1.5744</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>3.2839</v>
+        <v>2.9415</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1684</v>
+        <v>1.7767</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1156</v>
+        <v>1.1648</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7498</v>
@@ -1156,13 +1156,13 @@
         <v>0.7411</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2751</v>
+        <v>0.9326</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0869</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1883</v>
+        <v>0.2375</v>
       </c>
       <c r="V9" t="n">
         <v>2.2027</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4917</v>
+        <v>2.6137</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9405</v>
+        <v>1.1364</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5512</v>
+        <v>1.4773</v>
       </c>
       <c r="G10" t="n">
         <v>2.2127</v>
@@ -1234,13 +1234,13 @@
         <v>1.4823</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0915</v>
+        <v>0.0305</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3283</v>
+        <v>-0.1324</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2368</v>
+        <v>0.1629</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>U. CHAGOYEN SALGUERO</t>
+          <t>R. VARELA SANCHEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.6464</v>
+        <v>1.6494</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.6771</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7144</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.148</v>
+        <v>2.034</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1131</v>
+        <v>1.3811</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2611</v>
+        <v>0.6529</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2409</v>
+        <v>2.3237</v>
       </c>
       <c r="K11" t="n">
-        <v>0.412</v>
+        <v>2.1471</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6529</v>
+        <v>0.1766</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0929</v>
+        <v>-0.2897</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2989</v>
+        <v>-0.766</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3917</v>
+        <v>0.4763</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5558999999999999</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.6676</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6091</v>
+        <v>1.0601</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5434</v>
+        <v>0.8363</v>
       </c>
       <c r="U11" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.2238</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6294</v>
+        <v>-1.2594</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6294</v>
+        <v>-0.63</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. LÓPEZ RUIZ</t>
+          <t>U. CHAGOYEN SALGUERO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9441000000000001</v>
+        <v>1.549</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.7361</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>0.8129</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9441000000000001</v>
+        <v>-0.148</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3221</v>
+        <v>0.1131</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6221</v>
+        <v>-0.2611</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9441000000000001</v>
+        <v>-0.2409</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3221</v>
+        <v>0.412</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6221</v>
+        <v>-0.6529</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>0.0929</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>-0.2989</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.3917</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>0.5117</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>0.3476</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>0.1641</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. VARELA SANCHEZ</t>
+          <t>J. LÓPEZ RUIZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7932</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3022</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0954</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2.034</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3811</v>
+        <v>0.3221</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6529</v>
+        <v>0.6221</v>
       </c>
       <c r="J13" t="n">
-        <v>2.3237</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>2.1471</v>
+        <v>0.3221</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1766</v>
+        <v>0.6221</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2897</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.766</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4763</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6676</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2039</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.143</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3469</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.2594</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. CALLE GÓMEZ</t>
+          <t>A. CALLE GOMEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,58 +1501,58 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6221</v>
+        <v>0.7916</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6221</v>
+        <v>-0.7657</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1.5574</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6221</v>
+        <v>-1.4719</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.4973</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6221</v>
+        <v>-1.9693</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6221</v>
+        <v>-0.6977</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1.095</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6221</v>
+        <v>-1.7927</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>-0.7743</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>-0.5977</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>-0.1766</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.1117</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.0382</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.3371</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.0436</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>0.2935</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. CALLE GOMEZ</t>
+          <t>A. CALLE GÓMEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5717</v>
+        <v>0.6221</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.0595</v>
+        <v>0.6221</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6312</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.4719</v>
+        <v>0.6221</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4973</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.9693</v>
+        <v>0.6221</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6977</v>
+        <v>0.6221</v>
       </c>
       <c r="K15" t="n">
-        <v>1.095</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.7927</v>
+        <v>0.6221</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7743</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5977</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1766</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1117</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0382</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1172</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7499</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3673</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,16 +1657,16 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>53.7357</v>
+        <v>53.73570000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>31.78810000000001</v>
+        <v>31.7883</v>
       </c>
       <c r="F16" t="n">
-        <v>21.94750000000001</v>
+        <v>21.9475</v>
       </c>
       <c r="G16" t="n">
-        <v>33.84340000000001</v>
+        <v>33.8434</v>
       </c>
       <c r="H16" t="n">
         <v>18.4827</v>
@@ -1705,13 +1705,13 @@
         <v>8.356400000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>7.6478</v>
+        <v>7.6477</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7088000000000001</v>
+        <v>0.7086</v>
       </c>
       <c r="V16" t="n">
-        <v>5.977200000000001</v>
+        <v>5.9772</v>
       </c>
       <c r="W16" t="n">
         <v>9.438799999999999</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9895</v>
+        <v>-2.4385</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4231</v>
+        <v>0.7376</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.4126</v>
+        <v>-3.176</v>
       </c>
       <c r="G18" t="n">
         <v>-0.015</v>
@@ -1858,13 +1858,13 @@
         <v>0.9264</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1047</v>
+        <v>-0.5537</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8133</v>
+        <v>0.1278</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.918</v>
+        <v>-0.6815</v>
       </c>
       <c r="V18" t="n">
         <v>-0.9433</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.5265</v>
+        <v>-3.2241</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4879</v>
+        <v>-1.39</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.0386</v>
+        <v>-1.8342</v>
       </c>
       <c r="G19" t="n">
         <v>-2.0052</v>
@@ -1936,13 +1936,13 @@
         <v>0.9264</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5213</v>
+        <v>-1.219</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6566</v>
+        <v>-0.5586</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8648</v>
+        <v>-0.6603</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.592</v>
+        <v>-3.2512</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6514</v>
+        <v>0.0341</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.9406</v>
+        <v>-3.2853</v>
       </c>
       <c r="G20" t="n">
         <v>-3.6569</v>
@@ -2014,13 +2014,13 @@
         <v>1.6676</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6762</v>
+        <v>-0.3354</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7697000000000001</v>
+        <v>-0.0842</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0935</v>
+        <v>-0.2512</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6027</v>
+        <v>-3.5775</v>
       </c>
       <c r="E21" t="n">
-        <v>0.06510000000000001</v>
+        <v>-0.0328</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.6678</v>
+        <v>-3.5446</v>
       </c>
       <c r="G21" t="n">
         <v>-5.3556</v>
@@ -2092,13 +2092,13 @@
         <v>1.8529</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7299</v>
+        <v>-0.7048</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4813</v>
+        <v>0.3834</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.2112</v>
+        <v>-1.0881</v>
       </c>
       <c r="V21" t="n">
         <v>0.63</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.0147</v>
+        <v>-5.9494</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5159</v>
+        <v>-1.7117</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.4988</v>
+        <v>-4.2377</v>
       </c>
       <c r="G22" t="n">
         <v>-3.9826</v>
@@ -2170,13 +2170,13 @@
         <v>1.297</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8294</v>
+        <v>-0.7641</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0584</v>
+        <v>-0.2543</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.771</v>
+        <v>-0.5099</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5733</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.6317</v>
+        <v>-6.0029</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3297</v>
+        <v>-2.0359</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.302</v>
+        <v>-3.967</v>
       </c>
       <c r="G23" t="n">
         <v>-4.0148</v>
@@ -2248,13 +2248,13 @@
         <v>1.4823</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.2289</v>
+        <v>-1.6001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9849</v>
+        <v>-0.6911</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.244</v>
+        <v>-0.909</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9439</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.3748</v>
+        <v>-8.4757</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.378500000000001</v>
+        <v>-7.9868</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9963</v>
+        <v>-0.4889</v>
       </c>
       <c r="G24" t="n">
         <v>-1.8609</v>
@@ -2326,13 +2326,13 @@
         <v>1.6676</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4736</v>
+        <v>-0.5745</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.332</v>
+        <v>0.0597</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.1416</v>
+        <v>-0.6342</v>
       </c>
       <c r="V24" t="n">
         <v>0.63</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-9.902900000000001</v>
+        <v>-9.553000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.9158</v>
+        <v>-2.5241</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.9871</v>
+        <v>-7.0289</v>
       </c>
       <c r="G25" t="n">
         <v>-6.7379</v>
@@ -2404,13 +2404,13 @@
         <v>2.2234</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3149</v>
+        <v>-0.965</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3357</v>
+        <v>0.056</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9792</v>
+        <v>-1.021</v>
       </c>
       <c r="V25" t="n">
         <v>-3.1471</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-10.045</v>
+        <v>-10.9017</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.1005</v>
+        <v>-7.9818</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.9445</v>
+        <v>-2.9199</v>
       </c>
       <c r="G26" t="n">
         <v>-7.1588</v>
@@ -2482,13 +2482,13 @@
         <v>1.8529</v>
       </c>
       <c r="S26" t="n">
-        <v>0.5226</v>
+        <v>-0.3342</v>
       </c>
       <c r="T26" t="n">
-        <v>1.1341</v>
+        <v>0.2528</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.6116</v>
+        <v>-0.587</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6294</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-53.73570000000001</v>
+        <v>-52.4299</v>
       </c>
       <c r="E27" t="n">
-        <v>-21.9474</v>
+        <v>-21.9473</v>
       </c>
       <c r="F27" t="n">
-        <v>-31.7883</v>
+        <v>-30.4825</v>
       </c>
       <c r="G27" t="n">
         <v>-33.8436</v>
@@ -2560,13 +2560,13 @@
         <v>13.8965</v>
       </c>
       <c r="S27" t="n">
-        <v>-8.356299999999999</v>
+        <v>-7.0508</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.7085999999999997</v>
+        <v>-0.7085</v>
       </c>
       <c r="U27" t="n">
-        <v>-7.647900000000001</v>
+        <v>-6.3422</v>
       </c>
       <c r="V27" t="n">
         <v>-5.977</v>
